--- a/backend/scripts/audit-output/expeditor-smoke/ex-5.1.9.xlsx
+++ b/backend/scripts/audit-output/expeditor-smoke/ex-5.1.9.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="505">
   <si>
     <t xml:space="preserve">Товарно-транспортная накладная: </t>
   </si>
@@ -2223,7 +2223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="33" customWidth="1"/>
@@ -2560,7 +2560,7 @@
     <mergeCell ref="C26:E26"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.4" top="0.5" bottom="0.1" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
 </worksheet>
 </file>
 
@@ -2571,7 +2571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:O676"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -19491,7 +19491,7 @@
     <mergeCell ref="L676:O676"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.4" top="0.5" bottom="0.1" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="default" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -19501,8 +19501,8 @@
     <pageSetUpPr fitToPage="1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AD135"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <dimension ref="A1:AN135"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="48" customWidth="1"/>
@@ -19512,7 +19512,7 @@
     <col min="7" max="8" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>335</v>
       </c>
@@ -19524,7 +19524,7 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>336</v>
       </c>
@@ -19536,7 +19536,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>338</v>
       </c>
@@ -19548,7 +19548,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" ht="30" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="30" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="42" t="s">
         <v>5</v>
       </c>
@@ -19568,7 +19568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="43"/>
       <c r="B5" s="43" t="s">
         <v>341</v>
@@ -19578,7 +19578,7 @@
       <c r="E5" s="43"/>
       <c r="F5" s="43"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>1</v>
       </c>
@@ -19596,7 +19596,7 @@
         <v>127500</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>2</v>
       </c>
@@ -19614,7 +19614,7 @@
         <v>76500</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>3</v>
       </c>
@@ -19626,7 +19626,7 @@
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>4</v>
       </c>
@@ -19644,7 +19644,7 @@
         <v>25500</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>5</v>
       </c>
@@ -19662,7 +19662,7 @@
         <v>586500</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>6</v>
       </c>
@@ -19680,7 +19680,7 @@
         <v>331500</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="44"/>
       <c r="B12" s="44" t="s">
         <v>29</v>
@@ -19696,7 +19696,7 @@
         <v>1147500</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="43"/>
       <c r="B13" s="43" t="s">
         <v>348</v>
@@ -19706,7 +19706,7 @@
       <c r="E13" s="43"/>
       <c r="F13" s="43"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>1</v>
       </c>
@@ -19718,7 +19718,7 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>2</v>
       </c>
@@ -19736,7 +19736,7 @@
         <v>480000</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>3</v>
       </c>
@@ -19754,7 +19754,7 @@
         <v>864000</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>4</v>
       </c>
@@ -19766,7 +19766,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>5</v>
       </c>
@@ -19778,7 +19778,7 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
       <c r="B19" s="44" t="s">
         <v>29</v>
@@ -19794,7 +19794,7 @@
         <v>1344000</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="43"/>
       <c r="B20" s="43" t="s">
         <v>351</v>
@@ -19804,7 +19804,7 @@
       <c r="E20" s="43"/>
       <c r="F20" s="43"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>1</v>
       </c>
@@ -19816,7 +19816,7 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>2</v>
       </c>
@@ -19834,7 +19834,7 @@
         <v>910800</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>3</v>
       </c>
@@ -19852,7 +19852,7 @@
         <v>309600</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>4</v>
       </c>
@@ -19870,7 +19870,7 @@
         <v>4837500</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
       <c r="B25" s="44" t="s">
         <v>29</v>
@@ -19886,7 +19886,7 @@
         <v>6057900</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="43"/>
       <c r="B26" s="43" t="s">
         <v>356</v>
@@ -19896,7 +19896,7 @@
       <c r="E26" s="43"/>
       <c r="F26" s="43"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>1</v>
       </c>
@@ -19914,7 +19914,7 @@
         <v>1182500</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>2</v>
       </c>
@@ -19932,7 +19932,7 @@
         <v>605000</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>3</v>
       </c>
@@ -19950,7 +19950,7 @@
         <v>640000</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>4</v>
       </c>
@@ -21454,6 +21454,6 @@
     <mergeCell ref="C57:F57"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.1" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="default" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>